--- a/光伏配储项目/电价数据/2026/潮州站.xlsx
+++ b/光伏配储项目/电价数据/2026/潮州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.3391</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.77851</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07740999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.07991</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.18991</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17519</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25645</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26102</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.91952</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.53295</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60968</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5913099999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.76188</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14688</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43598</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67602</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9048200000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.55171</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.2261</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.43504</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.08229</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.09149</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.32885</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.39791</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46496</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7253099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7802100000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.82163</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86041</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7389</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49552</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.46095</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.41631</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71389</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.65448</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.89435</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.87325</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.48943</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5038</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.49625</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49198</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.52849</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.53066</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6807799999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.64236</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.22898</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.75747</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5382100000000001</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44544</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39416</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7119</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.18441</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6676799999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.97224</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.15427</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.38419</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.22578</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9999600000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.37079</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20765</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.42211</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06713</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.19227</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8428300000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.09918</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.01837</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.04765</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.91006</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.1558</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.98278</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47311</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9116000000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9177799999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47082</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46454</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33433</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5136799999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49225</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49062</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.46746</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.15446</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19265</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.1131</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9133600000000001</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7362799999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.72317</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.9460299999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.94224</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.96457</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.93765</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.82638</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.82666</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.83541</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.0553</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.58369</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.65406</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9327000000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.91111</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.7443099999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.81123</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5547300000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.9976</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.5502100000000001</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45745</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51549</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5360900000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6750900000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.72581</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.68959</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.66992</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.74605</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6664600000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7007599999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49168</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.66422</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.86949</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.12071</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47951</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.66183</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.48364</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.6085900000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.75995</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.95186</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6543300000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.14069</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.83278</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57604</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71528</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45422</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47689</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34185</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43316</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44073</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42633</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44777</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.76859</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.4744</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.74601</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.42497</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.77367</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.44546</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.58854</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.67576</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.96758</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.6771900000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.65154</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.5272899999999999</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41901</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.56067</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6609400000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.8264400000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.58677</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66149</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6255299999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.49086</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37601</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37475</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14322</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02337</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.45239</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24229</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10756</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03462</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44134</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31638</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23577</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24284</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25704</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18798</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.18129</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24611</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21189</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18948</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17046</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19771</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09605</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03946</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04916</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008539999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43183</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48387</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78799</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87029</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65183</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57148</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58365</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.63113</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.94404</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.54903</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43614</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7327</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.9724700000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26501</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.74595</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.5912000000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26124</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26075</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25998</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3228</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.83241</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.56053</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.60791</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.48425</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23064</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.53047</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.6365700000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.49085</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.4841</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.6228899999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.48794</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.45376</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.48735</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.50214</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.34493</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.30439</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.57233</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.71756</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.00468</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.89737</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.96572</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.53853</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5881799999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.46026</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.47435</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5578200000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.44307</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.46539</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16993</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.01088</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.43552</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.40699</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.46737</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5251399999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30831</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18368</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20512</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28689</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.23475</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.22896</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18232</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20384</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17947</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.22133</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.21587</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24738</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27928</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24677</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27961</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29408</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29851</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29393</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28736</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.44233</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28559</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30265</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08135</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49008</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48695</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43796</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49783</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43033</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5537300000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43996</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.43345</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.76276</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.56077</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.54149</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.47158</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.61536</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5935</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5834400000000001</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.84382</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5208700000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.43972</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.26348</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19462</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18703</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27285</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27557</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18879</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18618</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14901</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26044</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18591</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19165</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19818</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16172</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15333</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.24667</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.40528</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28339</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.24387</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.21978</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23122</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31975</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.02692</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28177</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27117</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26937</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19982</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29537</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44174</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.62579</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.58723</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6333200000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.77891</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31298</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28824</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44469</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47764</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51713</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37749</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.7301799999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8342200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.49166</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.69652</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5651499999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31168</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.01323</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27297</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27265</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.46622</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.58343</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.44663</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.5130800000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.45995</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34709</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.29824</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22472</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16143</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01476</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26629</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01722</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.01661</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16167</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02855</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19573</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16046</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01685</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15132</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15572</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19168</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15343</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15607</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15872</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01719</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16136</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01729</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04316</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17783</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21805</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.47929</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.0007099999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21482</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24143</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26379</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26131</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.20321</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.19527</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.21027</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.29652</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03226</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18035</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17745</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26407</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02988</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19671</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21844</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20984</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.04211</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.02763</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.02764</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.02788</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.02788</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.02774</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.04221</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.02788</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.02787</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.02707</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02315</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.22024</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00594</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04352</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.01895</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02635</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.03743</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03097</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.24069</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.02708</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26528</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.01318</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27607</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27395</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15544</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15967</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15716</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15337</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14274</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.02414</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.02311</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.02141</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18307</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2724</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22771</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8563999999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08899</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.02634</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24519</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.55736</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00186</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06942</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47542</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50434</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7455000000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.89638</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58102</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.76498</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7632100000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7669400000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8544400000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30434</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26315</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18097</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24243</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.20886</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.24532</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19489</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15809</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15282</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14667</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17225</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22383</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23376</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24255</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24856</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27238</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25868</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28811</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29778</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5539700000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45246</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.17701</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.76983</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7739400000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5221699999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64864</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8113400000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.54049</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19835</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31393</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49314</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50168</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.00696</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.77451</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53296</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6761</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54928</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6515299999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.61163</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.95102</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.78146</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5651900000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31855</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28654</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5416</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19837</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.46968</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.63064</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67274</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5345</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32235</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.67337</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44223</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41828</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45812</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.76586</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.79375</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.65083</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.85024</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.55222</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5831000000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.49657</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33654</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14579</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.1987</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14683</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04804</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12185</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22641</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14327</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14564</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18743</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18769</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.22741</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.43014</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.7295499999999999</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.8305399999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.57032</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.38388</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.62488</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6961499999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.45357</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5164299999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.77059</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6409400000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.79943</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.18042</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.84748</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.77328</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.76973</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6363099999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.46049</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43257</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36691</v>
       </c>
     </row>
   </sheetData>
